--- a/public/templates/catalog-import-01.xlsx
+++ b/public/templates/catalog-import-01.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R0ff91eddf1754839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_胶管主数据" sheetId="2" r:id="Rf75be01597244c3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="Rb392c832b58a4413"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R52b8a0324ab6472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R6ba61ec4cbef480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_胶管主数据" sheetId="2" r:id="Rb171d7fc3bc54c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="Ra49a54e314294b8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R3e380b8683e241ef"/>
   </x:sheets>
 </x:workbook>
 </file>
